--- a/files/九龙-启德-天玺．海第2A期.xlsx
+++ b/files/九龙-启德-天玺．海第2A期.xlsx
@@ -1262,7 +1262,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-04-16</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2025-07-18</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1662,7 +1662,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-05-15</t>
+          <t>2025-05-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2672,7 +2672,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -3908,7 +3908,7 @@
           <t>B | 1124呎 (4+房)
 $5058万
 $45,000/呎
-(26年-06月-16日)</t>
+(26年-06月-17日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr"/>
@@ -3924,7 +3924,7 @@
           <t>A | 1150呎 (4+房)
 $4164万
 $36,211/呎
-(25年-04月-13日)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -3932,7 +3932,7 @@
           <t>B | 1124呎 (4+房)
 $3960万
 $35,231/呎
-(25年-04月-15日)</t>
+(25年-04月-16日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr"/>
@@ -3948,7 +3948,7 @@
           <t>A | 1150呎 (4+房)
 $4298万
 $37,370/呎
-(25年-07月-17日)</t>
+(25年-07月-18日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -3956,7 +3956,7 @@
           <t>B | 1124呎 (4+房)
 $4258万
 $37,880/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr"/>
@@ -3972,7 +3972,7 @@
           <t>A | 1150呎 (4+房)
 $4095万
 $35,609/呎
-(25年-04月-14日)</t>
+(25年-04月-15日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -3980,7 +3980,7 @@
           <t>B | 1124呎 (4+房)
 $4520万
 $40,216/呎
-(26年-02月-23日)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr"/>
@@ -4028,7 +4028,7 @@
           <t>B | 1124呎 (4+房)
 $4252万
 $37,833/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr"/>
@@ -4044,7 +4044,7 @@
           <t>A | 1150呎 (4+房)
 $4000万
 $34,783/呎
-(25年-05月-15日)</t>
+(25年-05月-16日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -4052,7 +4052,7 @@
           <t>B | 1124呎 (4+房)
 $4228万
 $37,617/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr"/>
@@ -4076,7 +4076,7 @@
           <t>B | 1124呎 (4+房)
 $4019万
 $35,759/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr"/>
@@ -4092,7 +4092,7 @@
           <t>A | 1150呎 (4+房)
 $4889万
 $42,513/呎
-(26年-06月-25日)</t>
+(26年-06月-26日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -4100,7 +4100,7 @@
           <t>B | 1124呎 (4+房)
 $4407万
 $39,204/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr"/>
@@ -4124,7 +4124,7 @@
           <t>B | 1124呎 (4+房)
 $4113万
 $36,590/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr"/>
@@ -4140,7 +4140,7 @@
           <t>A | 1150呎 (4+房)
 $4866万
 $42,313/呎
-(26年-06月-24日)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -4148,7 +4148,7 @@
           <t>B | 1124呎 (4+房)
 $4251万
 $37,816/呎
-(26年-03月-04日)</t>
+(26年-03月-05日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr"/>
@@ -4172,7 +4172,7 @@
           <t>B | 1124呎 (4+房)
 $4447万
 $39,566/呎
-(26年-04月-19日)</t>
+(26年-04月-20日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr"/>

--- a/files/九龙-启德-天玺．海第2A期.xlsx
+++ b/files/九龙-启德-天玺．海第2A期.xlsx
@@ -2531,7 +2531,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -2556,12 +2556,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3754,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -4111,12 +4111,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">

--- a/files/九龙-启德-天玺．海第2A期.xlsx
+++ b/files/九龙-启德-天玺．海第2A期.xlsx
@@ -2531,23 +2531,19 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>51280000</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>44591</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2556,12 +2552,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -2571,7 +2567,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3750,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -3764,7 +3760,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -4111,12 +4107,12 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 1150呎 (4+房)
-招标单位
--
-(在售)</t>
+$5128万
+$44,591/呎
+(26年-08月-20日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
